--- a/Team-Data/2007-08/12-22-2007-08.xlsx
+++ b/Team-Data/2007-08/12-22-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>-0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -772,10 +839,10 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -784,22 +851,22 @@
         <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
         <v>22</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7</v>
       </c>
       <c r="AY2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>6</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,7 +1012,7 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
         <v>10</v>
@@ -966,25 +1033,25 @@
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
         <v>12</v>
@@ -993,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.417</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="J4" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="L4" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="O4" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="P4" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="R4" t="n">
         <v>11.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="T4" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V4" t="n">
         <v>16.3</v>
@@ -1088,43 +1155,43 @@
         <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="AA4" t="n">
         <v>21.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="AC4" t="n">
         <v>-5</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1133,13 +1200,13 @@
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
         <v>30</v>
@@ -1154,25 +1221,25 @@
         <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW4" t="n">
         <v>9</v>
       </c>
       <c r="AX4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA4" t="n">
         <v>16</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -1207,91 +1274,91 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.36</v>
+        <v>0.375</v>
       </c>
       <c r="H5" t="n">
         <v>48.2</v>
       </c>
       <c r="I5" t="n">
-        <v>35.1</v>
+        <v>34.8</v>
       </c>
       <c r="J5" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.413</v>
+        <v>0.411</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.323</v>
+        <v>0.321</v>
       </c>
       <c r="O5" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="P5" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.757</v>
+        <v>0.755</v>
       </c>
       <c r="R5" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="S5" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V5" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W5" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>92</v>
+        <v>91.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.8</v>
+        <v>-4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE5" t="n">
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>24</v>
@@ -1300,7 +1367,7 @@
         <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1330,28 +1397,28 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
         <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>14</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
@@ -1360,7 +1427,7 @@
         <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>-4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
         <v>18</v>
@@ -1497,10 +1564,10 @@
         <v>11</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
@@ -1509,7 +1576,7 @@
         <v>24</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>16</v>
@@ -1521,7 +1588,7 @@
         <v>27</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>17</v>
@@ -1542,7 +1609,7 @@
         <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1661,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>13</v>
@@ -1676,31 +1743,31 @@
         <v>18</v>
       </c>
       <c r="AM7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
         <v>16</v>
       </c>
       <c r="AU7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV7" t="n">
         <v>4</v>
@@ -1709,7 +1776,7 @@
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1718,7 +1785,7 @@
         <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1855,13 +1922,13 @@
         <v>12</v>
       </c>
       <c r="AL8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>19</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
@@ -1885,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2031,7 +2098,7 @@
         <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
         <v>8</v>
@@ -2043,7 +2110,7 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
@@ -2055,13 +2122,13 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT9" t="n">
         <v>21</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -2117,97 +2184,97 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>0.556</v>
+        <v>0.577</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="J10" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.448</v>
+        <v>0.451</v>
       </c>
       <c r="L10" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M10" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.347</v>
+        <v>0.351</v>
       </c>
       <c r="O10" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P10" t="n">
         <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.731</v>
+        <v>0.727</v>
       </c>
       <c r="R10" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U10" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y10" t="n">
         <v>5.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.3</v>
+        <v>108.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>9</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2225,28 +2292,28 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP10" t="n">
         <v>17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
         <v>6</v>
@@ -2255,22 +2322,22 @@
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY10" t="n">
         <v>26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2366,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.481</v>
+        <v>0.462</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>36.1</v>
+        <v>35.7</v>
       </c>
       <c r="J11" t="n">
-        <v>82.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R11" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="S11" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="V11" t="n">
         <v>14.7</v>
@@ -2359,40 +2426,40 @@
         <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
         <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ11" t="n">
         <v>11</v>
@@ -2404,13 +2471,13 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2419,37 +2486,37 @@
         <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS11" t="n">
         <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -2481,43 +2548,43 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
         <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.536</v>
+        <v>0.519</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N12" t="n">
         <v>0.36</v>
       </c>
       <c r="O12" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
         <v>0.752</v>
@@ -2526,52 +2593,52 @@
         <v>11.9</v>
       </c>
       <c r="S12" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T12" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U12" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="V12" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="W12" t="n">
         <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.5</v>
+        <v>104.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2589,13 +2656,13 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
         <v>16</v>
@@ -2604,19 +2671,19 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
         <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -2663,91 +2730,91 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
         <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.346</v>
+        <v>0.36</v>
       </c>
       <c r="H13" t="n">
         <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="J13" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.423</v>
+        <v>0.421</v>
       </c>
       <c r="L13" t="n">
         <v>5.3</v>
       </c>
       <c r="M13" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.356</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="P13" t="n">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0.78</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T13" t="n">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
       <c r="U13" t="n">
         <v>20.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z13" t="n">
         <v>22.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>24</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2771,13 +2838,13 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>8</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
         <v>7</v>
@@ -2786,37 +2853,37 @@
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
         <v>21</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2944,16 +3011,16 @@
         <v>12</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2965,7 +3032,7 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
         <v>2</v>
@@ -2983,10 +3050,10 @@
         <v>5</v>
       </c>
       <c r="AX14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY14" t="n">
         <v>15</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>20</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.296</v>
+        <v>0.308</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3045,10 +3112,10 @@
         <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L15" t="n">
         <v>8.1</v>
@@ -3060,70 +3127,70 @@
         <v>0.375</v>
       </c>
       <c r="O15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P15" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.76</v>
+        <v>0.765</v>
       </c>
       <c r="R15" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U15" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="V15" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="W15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.8</v>
+        <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
@@ -3153,31 +3220,31 @@
         <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
         <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
         <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -3209,106 +3276,106 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.296</v>
+        <v>0.269</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.5</v>
+        <v>35.3</v>
       </c>
       <c r="J16" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O16" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P16" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.709</v>
+        <v>0.704</v>
       </c>
       <c r="R16" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="T16" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V16" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W16" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
         <v>3.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="AA16" t="n">
         <v>22.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>-4.1</v>
+        <v>-4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3323,7 +3390,7 @@
         <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
@@ -3332,19 +3399,19 @@
         <v>27</v>
       </c>
       <c r="AS16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT16" t="n">
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV16" t="n">
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
         <v>4</v>
@@ -3353,16 +3420,16 @@
         <v>2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
         <v>10</v>
       </c>
       <c r="BB16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC16" t="n">
         <v>22</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -3391,94 +3458,94 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.423</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
-        <v>80.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L17" t="n">
         <v>5.3</v>
       </c>
       <c r="M17" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="O17" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R17" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T17" t="n">
         <v>41.5</v>
       </c>
       <c r="U17" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W17" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="X17" t="n">
         <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF17" t="n">
         <v>20</v>
       </c>
-      <c r="AF17" t="n">
-        <v>19</v>
-      </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
@@ -3487,13 +3554,13 @@
         <v>17</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>23</v>
@@ -3511,40 +3578,40 @@
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -3573,46 +3640,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
-        <v>0.154</v>
+        <v>0.16</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J18" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.439</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
         <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="P18" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.727</v>
+        <v>0.731</v>
       </c>
       <c r="R18" t="n">
         <v>12.4</v>
@@ -3624,34 +3691,34 @@
         <v>41.8</v>
       </c>
       <c r="U18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="W18" t="n">
         <v>7.3</v>
       </c>
       <c r="X18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.5</v>
+        <v>-7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,22 +3733,22 @@
         <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>19</v>
       </c>
       <c r="AM18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN18" t="n">
         <v>18</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,7 +3757,7 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
@@ -3705,7 +3772,7 @@
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>19</v>
@@ -3714,7 +3781,7 @@
         <v>22</v>
       </c>
       <c r="AY18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3723,10 +3790,10 @@
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.444</v>
+        <v>0.423</v>
       </c>
       <c r="H19" t="n">
         <v>48.6</v>
@@ -3773,10 +3840,10 @@
         <v>32.7</v>
       </c>
       <c r="J19" t="n">
-        <v>76.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -3788,64 +3855,64 @@
         <v>0.315</v>
       </c>
       <c r="O19" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P19" t="n">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.733</v>
+        <v>0.74</v>
       </c>
       <c r="R19" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="T19" t="n">
-        <v>41.7</v>
+        <v>41.1</v>
       </c>
       <c r="U19" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="V19" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="W19" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>91.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5</v>
+        <v>-5.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3866,34 +3933,34 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW19" t="n">
         <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -3937,85 +4004,85 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>0.63</v>
+        <v>0.615</v>
       </c>
       <c r="H20" t="n">
         <v>48.6</v>
       </c>
       <c r="I20" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="J20" t="n">
         <v>83</v>
       </c>
       <c r="K20" t="n">
-        <v>0.442</v>
+        <v>0.438</v>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M20" t="n">
         <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.368</v>
+        <v>0.374</v>
       </c>
       <c r="O20" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P20" t="n">
         <v>19.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.788</v>
+        <v>0.785</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T20" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U20" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W20" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="AA20" t="n">
         <v>19.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.3</v>
+        <v>95.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>7</v>
@@ -4027,25 +4094,25 @@
         <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL20" t="n">
         <v>8</v>
       </c>
-      <c r="AK20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>9</v>
-      </c>
       <c r="AM20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -4054,34 +4121,34 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT20" t="n">
         <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
         <v>27</v>
       </c>
       <c r="AY20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,10 +4276,10 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ21" t="n">
         <v>15</v>
@@ -4233,13 +4300,13 @@
         <v>16</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>29</v>
       </c>
       <c r="AR21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4254,25 +4321,25 @@
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ21" t="n">
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
         <v>6</v>
@@ -4400,7 +4467,7 @@
         <v>21</v>
       </c>
       <c r="AK22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL22" t="n">
         <v>2</v>
@@ -4409,13 +4476,13 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="n">
         <v>27</v>
@@ -4430,22 +4497,22 @@
         <v>7</v>
       </c>
       <c r="AU22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV22" t="n">
         <v>15</v>
       </c>
-      <c r="AV22" t="n">
-        <v>17</v>
-      </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
         <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -4483,121 +4550,121 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
         <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>0.407</v>
+        <v>0.385</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J23" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L23" t="n">
         <v>4.3</v>
       </c>
       <c r="M23" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P23" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R23" t="n">
         <v>12.7</v>
       </c>
       <c r="S23" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="V23" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z23" t="n">
         <v>20.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.59999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>20</v>
       </c>
-      <c r="AF23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>19</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>28</v>
       </c>
       <c r="AM23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO23" t="n">
         <v>21</v>
       </c>
       <c r="AP23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ23" t="n">
         <v>25</v>
@@ -4606,34 +4673,34 @@
         <v>5</v>
       </c>
       <c r="AS23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AW23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AY23" t="n">
         <v>12</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -4665,88 +4732,88 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.704</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="J24" t="n">
         <v>85.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.494</v>
+        <v>0.492</v>
       </c>
       <c r="L24" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.37</v>
+        <v>0.367</v>
       </c>
       <c r="O24" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.786</v>
+        <v>0.789</v>
       </c>
       <c r="R24" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T24" t="n">
         <v>40.7</v>
       </c>
       <c r="U24" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="V24" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="W24" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="X24" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.5</v>
+        <v>109</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="n">
         <v>4</v>
@@ -4767,28 +4834,28 @@
         <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM24" t="n">
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO24" t="n">
         <v>25</v>
       </c>
       <c r="AP24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT24" t="n">
         <v>26</v>
@@ -4797,10 +4864,10 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW24" t="n">
         <v>6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4818,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -4925,22 +4992,22 @@
         <v>-1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ25" t="n">
         <v>26</v>
@@ -4952,7 +5019,7 @@
         <v>15</v>
       </c>
       <c r="AM25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN25" t="n">
         <v>4</v>
@@ -4967,7 +5034,7 @@
         <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
         <v>26</v>
@@ -4976,7 +5043,7 @@
         <v>29</v>
       </c>
       <c r="AU25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
         <v>10</v>
@@ -4991,10 +5058,10 @@
         <v>3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -5107,28 +5174,28 @@
         <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ26" t="n">
         <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
         <v>17</v>
@@ -5161,10 +5228,10 @@
         <v>29</v>
       </c>
       <c r="AV26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>29</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -5211,94 +5278,94 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
         <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.731</v>
+        <v>0.72</v>
       </c>
       <c r="H27" t="n">
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J27" t="n">
         <v>80</v>
       </c>
       <c r="K27" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M27" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="N27" t="n">
         <v>0.39</v>
       </c>
       <c r="O27" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P27" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0.769</v>
       </c>
       <c r="R27" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="T27" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="U27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V27" t="n">
         <v>12.7</v>
       </c>
       <c r="W27" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
         <v>99.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
         <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
@@ -5307,13 +5374,13 @@
         <v>7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM27" t="n">
         <v>6</v>
@@ -5325,34 +5392,34 @@
         <v>27</v>
       </c>
       <c r="AP27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ27" t="n">
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ27" t="n">
         <v>2</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -5471,19 +5538,19 @@
         <v>-6.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5498,16 +5565,16 @@
         <v>26</v>
       </c>
       <c r="AM28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>8</v>
@@ -5522,7 +5589,7 @@
         <v>4</v>
       </c>
       <c r="AU28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -5575,82 +5642,82 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
         <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>0.517</v>
+        <v>0.536</v>
       </c>
       <c r="H29" t="n">
         <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J29" t="n">
-        <v>83</v>
+        <v>82.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L29" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.426</v>
+        <v>0.432</v>
       </c>
       <c r="O29" t="n">
-        <v>15.7</v>
+        <v>15.3</v>
       </c>
       <c r="P29" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="S29" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U29" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="V29" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="W29" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA29" t="n">
         <v>17.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
         <v>1</v>
@@ -5659,16 +5726,16 @@
         <v>9</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>10</v>
@@ -5695,25 +5762,25 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5728,7 +5795,7 @@
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -5757,49 +5824,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
         <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>0.517</v>
+        <v>0.536</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.487</v>
+        <v>0.488</v>
       </c>
       <c r="L30" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="M30" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O30" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="P30" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S30" t="n">
         <v>29</v>
@@ -5808,31 +5875,31 @@
         <v>41.6</v>
       </c>
       <c r="U30" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="V30" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W30" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.9</v>
+        <v>105</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,10 +5908,10 @@
         <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5865,13 +5932,13 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
@@ -5883,19 +5950,19 @@
         <v>28</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY30" t="n">
         <v>30</v>
@@ -5910,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
@@ -5939,103 +6006,103 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
         <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>37.1</v>
+        <v>37.4</v>
       </c>
       <c r="J31" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L31" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M31" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.339</v>
+        <v>0.343</v>
       </c>
       <c r="O31" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P31" t="n">
         <v>24.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.784</v>
+        <v>0.788</v>
       </c>
       <c r="R31" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S31" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="T31" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="U31" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X31" t="n">
         <v>5.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA31" t="n">
         <v>20.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.90000000000001</v>
+        <v>100.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>8</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>9</v>
       </c>
       <c r="AK31" t="n">
         <v>17</v>
@@ -6044,10 +6111,10 @@
         <v>13</v>
       </c>
       <c r="AM31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="n">
         <v>13</v>
@@ -6056,40 +6123,40 @@
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR31" t="n">
         <v>7</v>
       </c>
       <c r="AS31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA31" t="n">
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-22-2007-08</t>
+          <t>2007-12-22</t>
         </is>
       </c>
     </row>
